--- a/artfynd/S 2590-2020 artfynd.xlsx
+++ b/artfynd/S 2590-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65133867</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134032</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533506</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1387,6 +1417,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1513,6 +1548,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1639,6 +1679,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974494</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974495</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1872,6 +1922,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1993,6 +2048,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533523</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2119,6 +2179,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2226,6 +2291,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386042</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2342,6 +2412,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741856</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2458,6 +2533,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6741857</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2572,6 +2652,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65133861</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2691,6 +2776,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134047</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2812,6 +2902,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533501</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2933,6 +3028,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533522</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3041,6 +3141,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78740803</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3167,6 +3272,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974879</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3293,6 +3403,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974881</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3400,6 +3515,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386013</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3516,6 +3636,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/193795</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3635,6 +3760,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134028</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3754,6 +3884,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134061</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3875,6 +4010,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533525</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3996,6 +4136,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533529</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4122,6 +4267,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975158</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4248,6 +4398,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975159</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4355,6 +4510,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386330</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4471,6 +4631,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/450210</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4592,6 +4757,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533526</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4718,6 +4888,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974568</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4834,6 +5009,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/434542</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4948,6 +5128,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65133865</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5069,6 +5254,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533500</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5195,6 +5385,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974506</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5311,6 +5506,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/599809</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5432,6 +5632,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537415</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5558,6 +5763,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974449</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5674,6 +5884,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2310673</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5790,6 +6005,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2310674</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5904,6 +6124,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65133857</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6023,6 +6248,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134024</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6142,6 +6372,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65134041</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6268,6 +6503,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974794</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6394,6 +6634,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974795</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6520,6 +6765,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974797</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6646,6 +6896,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974798</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6772,6 +7027,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974800</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6879,6 +7139,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128386162</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7000,6 +7265,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533502</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7121,6 +7391,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533505</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7242,6 +7517,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533508</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7363,6 +7643,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533524</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7484,6 +7769,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533527</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7596,6 +7886,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78741108</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7708,6 +8003,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13963684</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7822,6 +8122,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78740717</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7936,8 +8241,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78741836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>